--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N439"/>
+  <dimension ref="A1:N441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21512,6 +21512,102 @@
         <v>330.29</v>
       </c>
       <c r="N439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>343.17</v>
+      </c>
+      <c r="C440" t="n">
+        <v>329.27</v>
+      </c>
+      <c r="D440" t="n">
+        <v>332.67</v>
+      </c>
+      <c r="E440" t="n">
+        <v>334.73</v>
+      </c>
+      <c r="F440" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="G440" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="H440" t="n">
+        <v>340.23</v>
+      </c>
+      <c r="I440" t="n">
+        <v>338.18</v>
+      </c>
+      <c r="J440" t="n">
+        <v>335.17</v>
+      </c>
+      <c r="K440" t="n">
+        <v>331.03</v>
+      </c>
+      <c r="L440" t="n">
+        <v>328.79</v>
+      </c>
+      <c r="M440" t="n">
+        <v>331.84</v>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>341.76</v>
+      </c>
+      <c r="C441" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="D441" t="n">
+        <v>332.08</v>
+      </c>
+      <c r="E441" t="n">
+        <v>334.01</v>
+      </c>
+      <c r="F441" t="n">
+        <v>339</v>
+      </c>
+      <c r="G441" t="n">
+        <v>343.06</v>
+      </c>
+      <c r="H441" t="n">
+        <v>340.04</v>
+      </c>
+      <c r="I441" t="n">
+        <v>338.02</v>
+      </c>
+      <c r="J441" t="n">
+        <v>334.99</v>
+      </c>
+      <c r="K441" t="n">
+        <v>331.22</v>
+      </c>
+      <c r="L441" t="n">
+        <v>328.76</v>
+      </c>
+      <c r="M441" t="n">
+        <v>332.34</v>
+      </c>
+      <c r="N441" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21528,7 +21624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B446"/>
+  <dimension ref="A1:B448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25991,6 +26087,26 @@
       </c>
       <c r="B446" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -26159,28 +26275,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7697728090170348</v>
+        <v>0.7675140434887383</v>
       </c>
       <c r="J2" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4160914892559424</v>
+        <v>0.4168591232876234</v>
       </c>
       <c r="M2" t="n">
-        <v>5.643776341790677</v>
+        <v>5.634081813350254</v>
       </c>
       <c r="N2" t="n">
-        <v>48.87622229060815</v>
+        <v>48.68725506298217</v>
       </c>
       <c r="O2" t="n">
-        <v>6.991153144554062</v>
+        <v>6.977625316895582</v>
       </c>
       <c r="P2" t="n">
-        <v>324.3027127666007</v>
+        <v>324.3265224881953</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26237,28 +26353,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6382501390042572</v>
+        <v>0.6358781452829662</v>
       </c>
       <c r="J3" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4615967369751464</v>
+        <v>0.4618560728826031</v>
       </c>
       <c r="M3" t="n">
-        <v>4.152032580869037</v>
+        <v>4.14848009129753</v>
       </c>
       <c r="N3" t="n">
-        <v>27.72115389196918</v>
+        <v>27.62964639512147</v>
       </c>
       <c r="O3" t="n">
-        <v>5.265088213123231</v>
+        <v>5.256391004778989</v>
       </c>
       <c r="P3" t="n">
-        <v>314.2820297440544</v>
+        <v>314.307168637715</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26315,28 +26431,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6598914897979117</v>
+        <v>0.6578885575203793</v>
       </c>
       <c r="J4" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K4" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5682200988979835</v>
+        <v>0.5688086522287146</v>
       </c>
       <c r="M4" t="n">
-        <v>3.335805829508731</v>
+        <v>3.334124997185199</v>
       </c>
       <c r="N4" t="n">
-        <v>19.30524870094163</v>
+        <v>19.2417360844452</v>
       </c>
       <c r="O4" t="n">
-        <v>4.393773856372404</v>
+        <v>4.386540332020806</v>
       </c>
       <c r="P4" t="n">
-        <v>316.8661539487982</v>
+        <v>316.8873804599471</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26393,28 +26509,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6140062763969247</v>
+        <v>0.6107064512796703</v>
       </c>
       <c r="J5" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K5" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6029605373339384</v>
+        <v>0.6016128359034039</v>
       </c>
       <c r="M5" t="n">
-        <v>2.902738845448902</v>
+        <v>2.909864567217035</v>
       </c>
       <c r="N5" t="n">
-        <v>14.5917349534777</v>
+        <v>14.59189557861918</v>
       </c>
       <c r="O5" t="n">
-        <v>3.819912951034054</v>
+        <v>3.819933975688477</v>
       </c>
       <c r="P5" t="n">
-        <v>321.6231759981258</v>
+        <v>321.6579535086839</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26471,28 +26587,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6099204291460357</v>
+        <v>0.6065230184966527</v>
       </c>
       <c r="J6" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K6" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6493422571535319</v>
+        <v>0.6476555867642362</v>
       </c>
       <c r="M6" t="n">
-        <v>2.802284434160151</v>
+        <v>2.810083455025369</v>
       </c>
       <c r="N6" t="n">
-        <v>11.80789964072973</v>
+        <v>11.82432350229339</v>
       </c>
       <c r="O6" t="n">
-        <v>3.436262452248042</v>
+        <v>3.438651407498787</v>
       </c>
       <c r="P6" t="n">
-        <v>326.715321913566</v>
+        <v>326.7511266873861</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26549,28 +26665,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6409965313758031</v>
+        <v>0.6396615807376899</v>
       </c>
       <c r="J7" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K7" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7510032175134295</v>
+        <v>0.7517552851972308</v>
       </c>
       <c r="M7" t="n">
-        <v>2.325153447678611</v>
+        <v>2.322107133586456</v>
       </c>
       <c r="N7" t="n">
-        <v>8.007184262334844</v>
+        <v>7.982933455399317</v>
       </c>
       <c r="O7" t="n">
-        <v>2.829696849900152</v>
+        <v>2.825408546635215</v>
       </c>
       <c r="P7" t="n">
-        <v>327.8395594246801</v>
+        <v>327.8536322923162</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26627,28 +26743,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6535501934691772</v>
+        <v>0.6486553721612146</v>
       </c>
       <c r="J8" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K8" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L8" t="n">
-        <v>0.678251038467347</v>
+        <v>0.6744259031719628</v>
       </c>
       <c r="M8" t="n">
-        <v>2.802506409159452</v>
+        <v>2.818663810921782</v>
       </c>
       <c r="N8" t="n">
-        <v>11.90970784005277</v>
+        <v>12.00057609105255</v>
       </c>
       <c r="O8" t="n">
-        <v>3.451044456400521</v>
+        <v>3.464184765720868</v>
       </c>
       <c r="P8" t="n">
-        <v>328.1694880893622</v>
+        <v>328.2210716465563</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26705,28 +26821,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6118043946425509</v>
+        <v>0.6066533358430531</v>
       </c>
       <c r="J9" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K9" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6636345218792198</v>
+        <v>0.6588066318928689</v>
       </c>
       <c r="M9" t="n">
-        <v>2.484979522862192</v>
+        <v>2.500996175973389</v>
       </c>
       <c r="N9" t="n">
-        <v>11.15126554783203</v>
+        <v>11.26113728305996</v>
       </c>
       <c r="O9" t="n">
-        <v>3.339351066873926</v>
+        <v>3.355761803683324</v>
       </c>
       <c r="P9" t="n">
-        <v>327.5630535082211</v>
+        <v>327.6173371537337</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26783,28 +26899,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6079351156313679</v>
+        <v>0.6030754543733852</v>
       </c>
       <c r="J10" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K10" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6624022178645319</v>
+        <v>0.6580912510280179</v>
       </c>
       <c r="M10" t="n">
-        <v>2.512345038691081</v>
+        <v>2.530356713808182</v>
       </c>
       <c r="N10" t="n">
-        <v>11.07155936287147</v>
+        <v>11.16415497317367</v>
       </c>
       <c r="O10" t="n">
-        <v>3.327395282029393</v>
+        <v>3.341280439169042</v>
       </c>
       <c r="P10" t="n">
-        <v>324.306982407047</v>
+        <v>324.3581953647455</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26861,28 +26977,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6279858358619966</v>
+        <v>0.6214739754112201</v>
       </c>
       <c r="J11" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K11" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6297973110715845</v>
+        <v>0.6228280071602654</v>
       </c>
       <c r="M11" t="n">
-        <v>2.703898766233512</v>
+        <v>2.727156919576562</v>
       </c>
       <c r="N11" t="n">
-        <v>13.52455480514128</v>
+        <v>13.71680424838408</v>
       </c>
       <c r="O11" t="n">
-        <v>3.677574581859799</v>
+        <v>3.703620424447418</v>
       </c>
       <c r="P11" t="n">
-        <v>321.6829350126735</v>
+        <v>321.7519361125725</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26939,28 +27055,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5685717442613437</v>
+        <v>0.5609927248281644</v>
       </c>
       <c r="J12" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K12" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5484270068367163</v>
+        <v>0.5387297997287497</v>
       </c>
       <c r="M12" t="n">
-        <v>3.084007965318173</v>
+        <v>3.114731625325292</v>
       </c>
       <c r="N12" t="n">
-        <v>15.52974012694176</v>
+        <v>15.80282030607129</v>
       </c>
       <c r="O12" t="n">
-        <v>3.94077912689125</v>
+        <v>3.975276129537581</v>
       </c>
       <c r="P12" t="n">
-        <v>322.1701911398237</v>
+        <v>322.2505011759933</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27017,28 +27133,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3303737586432844</v>
+        <v>0.3277404039461413</v>
       </c>
       <c r="J13" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K13" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3109115839002953</v>
+        <v>0.3089383808969764</v>
       </c>
       <c r="M13" t="n">
-        <v>2.915594131648561</v>
+        <v>2.914616743521144</v>
       </c>
       <c r="N13" t="n">
-        <v>14.11346495518309</v>
+        <v>14.09096124652698</v>
       </c>
       <c r="O13" t="n">
-        <v>3.756789181626125</v>
+        <v>3.753792914709997</v>
       </c>
       <c r="P13" t="n">
-        <v>326.2093693908947</v>
+        <v>326.2372711042432</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27076,7 +27192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N439"/>
+  <dimension ref="A1:N441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58667,6 +58783,150 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-42.50542907017297,173.50992137437825</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-42.50600301312664,173.5094412920336</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-42.50663213019335,173.50915812402624</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-42.50725696712573,173.50885970404414</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-42.50789302765902,173.50859023994224</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-42.50854249062794,173.50839068299322</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-42.50917589620168,173.50811901225907</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-42.50981795859586,173.5078839107785</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-42.510466655024395,173.50768472693508</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-42.511111367719444,173.50747269888137</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-42.511759555518104,173.50728356185388</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-42.51241658553404,173.5071623657452</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-42.50542457284811,173.50990532533527</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-42.505999919187055,173.50943025111917</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-42.506630248302756,173.50915140835605</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-42.50725467056795,173.5088515085751</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-42.50789168998851,173.50858481242793</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-42.508539943562226,173.5083779961558</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-42.50917548902924,173.50811676601543</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-42.509817665867104,173.50788200385432</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-42.5104663686434,173.5076825703959</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-42.51111166978306,173.50747497530688</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-42.51175950853885,173.50728320224258</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-42.512417357202274,173.50716836201138</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N441"/>
+  <dimension ref="A1:N443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21608,6 +21608,102 @@
         <v>332.34</v>
       </c>
       <c r="N441" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="C442" t="n">
+        <v>329.57</v>
+      </c>
+      <c r="D442" t="n">
+        <v>332.85</v>
+      </c>
+      <c r="E442" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="F442" t="n">
+        <v>339.58</v>
+      </c>
+      <c r="G442" t="n">
+        <v>343.24</v>
+      </c>
+      <c r="H442" t="n">
+        <v>340.75</v>
+      </c>
+      <c r="I442" t="n">
+        <v>338.83</v>
+      </c>
+      <c r="J442" t="n">
+        <v>335.93</v>
+      </c>
+      <c r="K442" t="n">
+        <v>331.97</v>
+      </c>
+      <c r="L442" t="n">
+        <v>329.71</v>
+      </c>
+      <c r="M442" t="n">
+        <v>333.27</v>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>343.27</v>
+      </c>
+      <c r="C443" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="D443" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="E443" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="F443" t="n">
+        <v>340.35</v>
+      </c>
+      <c r="G443" t="n">
+        <v>344.27</v>
+      </c>
+      <c r="H443" t="n">
+        <v>341.95</v>
+      </c>
+      <c r="I443" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="J443" t="n">
+        <v>337.14</v>
+      </c>
+      <c r="K443" t="n">
+        <v>332.89</v>
+      </c>
+      <c r="L443" t="n">
+        <v>330.44</v>
+      </c>
+      <c r="M443" t="n">
+        <v>334.26</v>
+      </c>
+      <c r="N443" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21624,7 +21720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B448"/>
+  <dimension ref="A1:B450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26107,6 +26203,26 @@
       </c>
       <c r="B448" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -26275,28 +26391,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7675140434887383</v>
+        <v>0.7658044358078266</v>
       </c>
       <c r="J2" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4168591232876234</v>
+        <v>0.4180357031062832</v>
       </c>
       <c r="M2" t="n">
-        <v>5.634081813350254</v>
+        <v>5.620636091067135</v>
       </c>
       <c r="N2" t="n">
-        <v>48.68725506298217</v>
+        <v>48.48490208855657</v>
       </c>
       <c r="O2" t="n">
-        <v>6.977625316895582</v>
+        <v>6.963110087350089</v>
       </c>
       <c r="P2" t="n">
-        <v>324.3265224881953</v>
+        <v>324.3445983755567</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26353,28 +26469,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6358781452829662</v>
+        <v>0.6346182211681247</v>
       </c>
       <c r="J3" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K3" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4618560728826031</v>
+        <v>0.4631854688904774</v>
       </c>
       <c r="M3" t="n">
-        <v>4.14848009129753</v>
+        <v>4.137791527730986</v>
       </c>
       <c r="N3" t="n">
-        <v>27.62964639512147</v>
+        <v>27.51495071688165</v>
       </c>
       <c r="O3" t="n">
-        <v>5.256391004778989</v>
+        <v>5.245469542079303</v>
       </c>
       <c r="P3" t="n">
-        <v>314.307168637715</v>
+        <v>314.3205582307963</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26431,28 +26547,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6578885575203793</v>
+        <v>0.6565629628607557</v>
       </c>
       <c r="J4" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K4" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5688086522287146</v>
+        <v>0.5700567791627567</v>
       </c>
       <c r="M4" t="n">
-        <v>3.334124997185199</v>
+        <v>3.327862511495034</v>
       </c>
       <c r="N4" t="n">
-        <v>19.2417360844452</v>
+        <v>19.16549668376479</v>
       </c>
       <c r="O4" t="n">
-        <v>4.386540332020806</v>
+        <v>4.377841555351768</v>
       </c>
       <c r="P4" t="n">
-        <v>316.8873804599471</v>
+        <v>316.9014706211568</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26509,28 +26625,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6107064512796703</v>
+        <v>0.6081487847804377</v>
       </c>
       <c r="J5" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K5" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6016128359034039</v>
+        <v>0.6012417455778879</v>
       </c>
       <c r="M5" t="n">
-        <v>2.909864567217035</v>
+        <v>2.912366959473575</v>
       </c>
       <c r="N5" t="n">
-        <v>14.59189557861918</v>
+        <v>14.56693045003633</v>
       </c>
       <c r="O5" t="n">
-        <v>3.819933975688477</v>
+        <v>3.816664833337652</v>
       </c>
       <c r="P5" t="n">
-        <v>321.6579535086839</v>
+        <v>321.6849922888438</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26587,28 +26703,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6065230184966527</v>
+        <v>0.6037776225490487</v>
       </c>
       <c r="J6" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K6" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6476555867642362</v>
+        <v>0.6468872431670529</v>
       </c>
       <c r="M6" t="n">
-        <v>2.810083455025369</v>
+        <v>2.814020325474651</v>
       </c>
       <c r="N6" t="n">
-        <v>11.82432350229339</v>
+        <v>11.81752820975833</v>
       </c>
       <c r="O6" t="n">
-        <v>3.438651407498787</v>
+        <v>3.437663190273057</v>
       </c>
       <c r="P6" t="n">
-        <v>326.7511266873861</v>
+        <v>326.780152044037</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26665,28 +26781,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6396615807376899</v>
+        <v>0.6384454852169076</v>
       </c>
       <c r="J7" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K7" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7517552851972308</v>
+        <v>0.7526099328671643</v>
       </c>
       <c r="M7" t="n">
-        <v>2.322107133586456</v>
+        <v>2.31851197318877</v>
       </c>
       <c r="N7" t="n">
-        <v>7.982933455399317</v>
+        <v>7.956970611314375</v>
       </c>
       <c r="O7" t="n">
-        <v>2.825408546635215</v>
+        <v>2.820810275668035</v>
       </c>
       <c r="P7" t="n">
-        <v>327.8536322923162</v>
+        <v>327.8664849187774</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26743,28 +26859,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6486553721612146</v>
+        <v>0.6448643208200551</v>
       </c>
       <c r="J8" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K8" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6744259031719628</v>
+        <v>0.6723333503777092</v>
       </c>
       <c r="M8" t="n">
-        <v>2.818663810921782</v>
+        <v>2.828150953639094</v>
       </c>
       <c r="N8" t="n">
-        <v>12.00057609105255</v>
+        <v>12.03572025018909</v>
       </c>
       <c r="O8" t="n">
-        <v>3.464184765720868</v>
+        <v>3.469253558071115</v>
       </c>
       <c r="P8" t="n">
-        <v>328.2210716465563</v>
+        <v>328.2611510600964</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26821,28 +26937,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6066533358430531</v>
+        <v>0.6028217636767189</v>
       </c>
       <c r="J9" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K9" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6588066318928689</v>
+        <v>0.6562872677346191</v>
       </c>
       <c r="M9" t="n">
-        <v>2.500996175973389</v>
+        <v>2.510181087580411</v>
       </c>
       <c r="N9" t="n">
-        <v>11.26113728305996</v>
+        <v>11.30231192231309</v>
       </c>
       <c r="O9" t="n">
-        <v>3.355761803683324</v>
+        <v>3.36189112291179</v>
       </c>
       <c r="P9" t="n">
-        <v>327.6173371537337</v>
+        <v>327.6578432740861</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26899,28 +27015,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6030754543733852</v>
+        <v>0.5995259693150066</v>
       </c>
       <c r="J10" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K10" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6580912510280179</v>
+        <v>0.6560212401699449</v>
       </c>
       <c r="M10" t="n">
-        <v>2.530356713808182</v>
+        <v>2.540389441040792</v>
       </c>
       <c r="N10" t="n">
-        <v>11.16415497317367</v>
+        <v>11.19225319446693</v>
       </c>
       <c r="O10" t="n">
-        <v>3.341280439169042</v>
+        <v>3.345482505479132</v>
       </c>
       <c r="P10" t="n">
-        <v>324.3581953647455</v>
+        <v>324.3957203904943</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26977,28 +27093,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6214739754112201</v>
+        <v>0.6161880767062988</v>
       </c>
       <c r="J11" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K11" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6228280071602654</v>
+        <v>0.6181769631367218</v>
       </c>
       <c r="M11" t="n">
-        <v>2.727156919576562</v>
+        <v>2.74461237526156</v>
       </c>
       <c r="N11" t="n">
-        <v>13.71680424838408</v>
+        <v>13.8245250254102</v>
       </c>
       <c r="O11" t="n">
-        <v>3.703620424447418</v>
+        <v>3.718134616364797</v>
       </c>
       <c r="P11" t="n">
-        <v>321.7519361125725</v>
+        <v>321.8081312269323</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27055,28 +27171,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5609927248281644</v>
+        <v>0.5546560665929894</v>
       </c>
       <c r="J12" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K12" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5387297997287497</v>
+        <v>0.5316708400964585</v>
       </c>
       <c r="M12" t="n">
-        <v>3.114731625325292</v>
+        <v>3.138366526518519</v>
       </c>
       <c r="N12" t="n">
-        <v>15.80282030607129</v>
+        <v>15.97460837214548</v>
       </c>
       <c r="O12" t="n">
-        <v>3.975276129537581</v>
+        <v>3.996824786270407</v>
       </c>
       <c r="P12" t="n">
-        <v>322.2505011759933</v>
+        <v>322.3178694474572</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27133,28 +27249,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3277404039461413</v>
+        <v>0.3265790287103148</v>
       </c>
       <c r="J13" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K13" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3089383808969764</v>
+        <v>0.3093531429832785</v>
       </c>
       <c r="M13" t="n">
-        <v>2.914616743521144</v>
+        <v>2.90676431339352</v>
       </c>
       <c r="N13" t="n">
-        <v>14.09096124652698</v>
+        <v>14.03629284376131</v>
       </c>
       <c r="O13" t="n">
-        <v>3.753792914709997</v>
+        <v>3.746504082976731</v>
       </c>
       <c r="P13" t="n">
-        <v>326.2372711042432</v>
+        <v>326.249612681095</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27192,7 +27308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N441"/>
+  <dimension ref="A1:N443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58927,6 +59043,150 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-42.505428368462844,173.5099188702721</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-42.506003970014945,173.50944470674963</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-42.5066327043294,173.50916017287486</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-42.50725687143583,173.50885936256626</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-42.5078933407308,173.50859151021157</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-42.50854036807327,173.50838011062862</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-42.50917701056818,173.5081251598734</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-42.50981914780612,173.50789165765815</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-42.51046786418811,173.50769383232287</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-42.511112862139065,173.50748396119715</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-42.51176099621455,173.5072945899344</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-42.51241879250433,173.50717951506692</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-42.5054293891321,173.50992251260834</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-42.50600709584936,173.50945586148936</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-42.50663471380524,173.5091673438453</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-42.50726006109845,173.50887074516308</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-42.507895532232894,173.5086004020973</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-42.50854279721908,173.5083922101126</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-42.50917958218188,173.50813934667647</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-42.50982181895339,173.50790905834276</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-42.510469789302576,173.50770832905943</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-42.51111432476147,173.5074949838897</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-42.511762139375115,173.50730334047688</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-42.51242032040531,173.50719138767496</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N443"/>
+  <dimension ref="A1:N444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21704,6 +21704,54 @@
         <v>334.26</v>
       </c>
       <c r="N443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>343</v>
+      </c>
+      <c r="C444" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="D444" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="E444" t="n">
+        <v>336.14</v>
+      </c>
+      <c r="F444" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="G444" t="n">
+        <v>345.48</v>
+      </c>
+      <c r="H444" t="n">
+        <v>343.03</v>
+      </c>
+      <c r="I444" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="J444" t="n">
+        <v>338.42</v>
+      </c>
+      <c r="K444" t="n">
+        <v>333.51</v>
+      </c>
+      <c r="L444" t="n">
+        <v>331.79</v>
+      </c>
+      <c r="M444" t="n">
+        <v>335.12</v>
+      </c>
+      <c r="N444" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21720,7 +21768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B450"/>
+  <dimension ref="A1:B451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26223,6 +26271,16 @@
       </c>
       <c r="B450" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -26391,28 +26449,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7658044358078266</v>
+        <v>0.7648891338291918</v>
       </c>
       <c r="J2" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K2" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4180357031062832</v>
+        <v>0.4185777007449051</v>
       </c>
       <c r="M2" t="n">
-        <v>5.620636091067135</v>
+        <v>5.614354462372345</v>
       </c>
       <c r="N2" t="n">
-        <v>48.48490208855657</v>
+        <v>48.38575310678635</v>
       </c>
       <c r="O2" t="n">
-        <v>6.963110087350089</v>
+        <v>6.955986853551863</v>
       </c>
       <c r="P2" t="n">
-        <v>324.3445983755567</v>
+        <v>324.3543098303072</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26469,28 +26527,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6346182211681247</v>
+        <v>0.6343560104796331</v>
       </c>
       <c r="J3" t="n">
+        <v>443</v>
+      </c>
+      <c r="K3" t="n">
         <v>442</v>
       </c>
-      <c r="K3" t="n">
-        <v>441</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.4631854688904774</v>
+        <v>0.4641779498480805</v>
       </c>
       <c r="M3" t="n">
-        <v>4.137791527730986</v>
+        <v>4.130105668200933</v>
       </c>
       <c r="N3" t="n">
-        <v>27.51495071688165</v>
+        <v>27.45353584687686</v>
       </c>
       <c r="O3" t="n">
-        <v>5.245469542079303</v>
+        <v>5.239612184778265</v>
       </c>
       <c r="P3" t="n">
-        <v>314.3205582307963</v>
+        <v>314.3233555415073</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26547,28 +26605,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6565629628607557</v>
+        <v>0.6561477434563644</v>
       </c>
       <c r="J4" t="n">
+        <v>443</v>
+      </c>
+      <c r="K4" t="n">
         <v>442</v>
       </c>
-      <c r="K4" t="n">
-        <v>441</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.5700567791627567</v>
+        <v>0.5709077998040397</v>
       </c>
       <c r="M4" t="n">
-        <v>3.327862511495034</v>
+        <v>3.323083865929747</v>
       </c>
       <c r="N4" t="n">
-        <v>19.16549668376479</v>
+        <v>19.12423254241281</v>
       </c>
       <c r="O4" t="n">
-        <v>4.377841555351768</v>
+        <v>4.373126174993446</v>
       </c>
       <c r="P4" t="n">
-        <v>316.9014706211568</v>
+        <v>316.9059002563254</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26625,28 +26683,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6081487847804377</v>
+        <v>0.6072678762940872</v>
       </c>
       <c r="J5" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K5" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6012417455778879</v>
+        <v>0.6015478629695566</v>
       </c>
       <c r="M5" t="n">
-        <v>2.912366959473575</v>
+        <v>2.911144475686765</v>
       </c>
       <c r="N5" t="n">
-        <v>14.56693045003633</v>
+        <v>14.54358637952753</v>
       </c>
       <c r="O5" t="n">
-        <v>3.816664833337652</v>
+        <v>3.813605430498484</v>
       </c>
       <c r="P5" t="n">
-        <v>321.6849922888438</v>
+        <v>321.6943388248551</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26703,28 +26761,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6037776225490487</v>
+        <v>0.6029273489357349</v>
       </c>
       <c r="J6" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K6" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6468872431670529</v>
+        <v>0.6471750665352765</v>
       </c>
       <c r="M6" t="n">
-        <v>2.814020325474651</v>
+        <v>2.812815532434468</v>
       </c>
       <c r="N6" t="n">
-        <v>11.81752820975833</v>
+        <v>11.79973857777192</v>
       </c>
       <c r="O6" t="n">
-        <v>3.437663190273057</v>
+        <v>3.435074755776346</v>
       </c>
       <c r="P6" t="n">
-        <v>326.780152044037</v>
+        <v>326.7891735406732</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26781,28 +26839,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6384454852169076</v>
+        <v>0.6385623476914052</v>
       </c>
       <c r="J7" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K7" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7526099328671643</v>
+        <v>0.7535725813917946</v>
       </c>
       <c r="M7" t="n">
-        <v>2.31851197318877</v>
+        <v>2.313845704717904</v>
       </c>
       <c r="N7" t="n">
-        <v>7.956970611314375</v>
+        <v>7.939176918738656</v>
       </c>
       <c r="O7" t="n">
-        <v>2.820810275668035</v>
+        <v>2.817654506631119</v>
       </c>
       <c r="P7" t="n">
-        <v>327.8664849187774</v>
+        <v>327.8652449950587</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26859,28 +26917,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6448643208200551</v>
+        <v>0.6436935541147085</v>
       </c>
       <c r="J8" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K8" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6723333503777092</v>
+        <v>0.6722883588609908</v>
       </c>
       <c r="M8" t="n">
-        <v>2.828150953639094</v>
+        <v>2.828577615979295</v>
       </c>
       <c r="N8" t="n">
-        <v>12.03572025018909</v>
+        <v>12.02539981058943</v>
       </c>
       <c r="O8" t="n">
-        <v>3.469253558071115</v>
+        <v>3.467765824070223</v>
       </c>
       <c r="P8" t="n">
-        <v>328.2611510600964</v>
+        <v>328.2735730237191</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26937,28 +26995,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6028217636767189</v>
+        <v>0.6019144616508901</v>
       </c>
       <c r="J9" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K9" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6562872677346191</v>
+        <v>0.6564954040486004</v>
       </c>
       <c r="M9" t="n">
-        <v>2.510181087580411</v>
+        <v>2.509376210144599</v>
       </c>
       <c r="N9" t="n">
-        <v>11.30231192231309</v>
+        <v>11.28691732984771</v>
       </c>
       <c r="O9" t="n">
-        <v>3.36189112291179</v>
+        <v>3.359600769414085</v>
       </c>
       <c r="P9" t="n">
-        <v>327.6578432740861</v>
+        <v>327.6674698484567</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27015,28 +27073,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5995259693150066</v>
+        <v>0.5985607468249592</v>
       </c>
       <c r="J10" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K10" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6560212401699449</v>
+        <v>0.6561531588170223</v>
       </c>
       <c r="M10" t="n">
-        <v>2.540389441040792</v>
+        <v>2.540525747899596</v>
       </c>
       <c r="N10" t="n">
-        <v>11.19225319446693</v>
+        <v>11.17844017334311</v>
       </c>
       <c r="O10" t="n">
-        <v>3.345482505479132</v>
+        <v>3.343417439289194</v>
       </c>
       <c r="P10" t="n">
-        <v>324.3957203904943</v>
+        <v>324.4059615073661</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27093,28 +27151,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6161880767062988</v>
+        <v>0.6140243977879879</v>
       </c>
       <c r="J11" t="n">
+        <v>443</v>
+      </c>
+      <c r="K11" t="n">
         <v>442</v>
       </c>
-      <c r="K11" t="n">
-        <v>441</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.6181769631367218</v>
+        <v>0.6166873486377917</v>
       </c>
       <c r="M11" t="n">
-        <v>2.74461237526156</v>
+        <v>2.75092314357877</v>
       </c>
       <c r="N11" t="n">
-        <v>13.8245250254102</v>
+        <v>13.85018145179346</v>
       </c>
       <c r="O11" t="n">
-        <v>3.718134616364797</v>
+        <v>3.721583191572298</v>
       </c>
       <c r="P11" t="n">
-        <v>321.8081312269323</v>
+        <v>321.8312137421734</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27171,28 +27229,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5546560665929894</v>
+        <v>0.5522530421344579</v>
       </c>
       <c r="J12" t="n">
+        <v>443</v>
+      </c>
+      <c r="K12" t="n">
         <v>442</v>
       </c>
-      <c r="K12" t="n">
-        <v>441</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.5316708400964585</v>
+        <v>0.5296205284514045</v>
       </c>
       <c r="M12" t="n">
-        <v>3.138366526518519</v>
+        <v>3.145640850929628</v>
       </c>
       <c r="N12" t="n">
-        <v>15.97460837214548</v>
+        <v>16.00869300162817</v>
       </c>
       <c r="O12" t="n">
-        <v>3.996824786270407</v>
+        <v>4.00108647764931</v>
       </c>
       <c r="P12" t="n">
-        <v>322.3178694474572</v>
+        <v>322.3435053439015</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27249,28 +27307,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3265790287103148</v>
+        <v>0.3265800333143166</v>
       </c>
       <c r="J13" t="n">
+        <v>443</v>
+      </c>
+      <c r="K13" t="n">
         <v>442</v>
       </c>
-      <c r="K13" t="n">
-        <v>441</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.3093531429832785</v>
+        <v>0.3103912023726413</v>
       </c>
       <c r="M13" t="n">
-        <v>2.90676431339352</v>
+        <v>2.900193836358914</v>
       </c>
       <c r="N13" t="n">
-        <v>14.03629284376131</v>
+        <v>14.0045365373839</v>
       </c>
       <c r="O13" t="n">
-        <v>3.746504082976731</v>
+        <v>3.742263557979836</v>
       </c>
       <c r="P13" t="n">
-        <v>326.249612681095</v>
+        <v>326.249601963799</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27308,7 +27366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N443"/>
+  <dimension ref="A1:N444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59187,6 +59245,78 @@
         </is>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-42.50542852794243,173.50991943938715</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-42.50600837169985,173.50946041444467</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-42.5066356388019,173.50917064476835</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-42.50726146454964,173.50887575350606</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-42.50789792296168,173.508610102337</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-42.50854565087416,173.5084064240707</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-42.50918189663271,173.50815211480023</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-42.50982478282603,173.5079283659534</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-42.51047182578528,173.5077236644511</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-42.51111531044119,173.50750241222627</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-42.511764253437384,173.50731952298779</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-42.51242164767185,173.50720170125413</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
